--- a/data.mn/public/datasets/livestock-total-mn.xlsx
+++ b/data.mn/public/datasets/livestock-total-mn.xlsx
@@ -455,15 +455,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22574.72</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22574.72</v>
       </c>
     </row>
     <row r="3">
@@ -477,15 +473,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>22692.57</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22692.57</v>
       </c>
     </row>
     <row r="4">
@@ -499,15 +491,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>23108.06</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23108.06</v>
       </c>
     </row>
     <row r="5">
@@ -521,15 +509,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>23538.01</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23538.01</v>
       </c>
     </row>
     <row r="6">
@@ -543,15 +527,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>24313.47</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24313.47</v>
       </c>
     </row>
     <row r="7">
@@ -565,15 +545,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>24351.58</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24351.58</v>
       </c>
     </row>
     <row r="8">
@@ -587,15 +563,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>23683.96</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23683.96</v>
       </c>
     </row>
     <row r="9">
@@ -609,15 +581,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>22942.12</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22942.12</v>
       </c>
     </row>
     <row r="10">
@@ -631,15 +599,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>24025.67</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24025.67</v>
       </c>
     </row>
     <row r="11">
@@ -653,15 +617,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>24201.2</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24201.2</v>
       </c>
     </row>
     <row r="12">
@@ -675,15 +635,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>23771.48</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23771.48</v>
       </c>
     </row>
     <row r="13">
@@ -697,15 +653,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>24263.07</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24263.07</v>
       </c>
     </row>
     <row r="14">
@@ -719,15 +671,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>24764.65</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24764.65</v>
       </c>
     </row>
     <row r="15">
@@ -741,15 +689,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>23570.32</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23570.32</v>
       </c>
     </row>
     <row r="16">
@@ -763,15 +707,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>22591.93</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22591.93</v>
       </c>
     </row>
     <row r="17">
@@ -785,15 +725,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>22485.49</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22485.49</v>
       </c>
     </row>
     <row r="18">
@@ -807,15 +743,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>22590.51</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22590.51</v>
       </c>
     </row>
     <row r="19">
@@ -829,15 +761,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>22741.1</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22741.1</v>
       </c>
     </row>
     <row r="20">
@@ -851,15 +779,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>23122.25</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23122.25</v>
       </c>
     </row>
     <row r="21">
@@ -873,15 +797,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>24674.93</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24674.93</v>
       </c>
     </row>
     <row r="22">
@@ -895,15 +815,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>25856.9</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25856.9</v>
       </c>
     </row>
     <row r="23">
@@ -917,15 +833,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>25527.91</t>
-        </is>
+      <c r="C23" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25527.91</v>
       </c>
     </row>
     <row r="24">
@@ -939,15 +851,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>25694.09</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25694.09</v>
       </c>
     </row>
     <row r="25">
@@ -961,15 +869,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>24688.34</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24688.34</v>
       </c>
     </row>
     <row r="26">
@@ -983,15 +887,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>26778.42</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26778.42</v>
       </c>
     </row>
     <row r="27">
@@ -1005,15 +905,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>28572.34</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D27" t="n">
+        <v>28572.34</v>
       </c>
     </row>
     <row r="28">
@@ -1027,15 +923,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>29300.14</t>
-        </is>
+      <c r="C28" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29300.14</v>
       </c>
     </row>
     <row r="29">
@@ -1049,15 +941,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>31292.32</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D29" t="n">
+        <v>31292.32</v>
       </c>
     </row>
     <row r="30">
@@ -1071,15 +959,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>32897.54</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D30" t="n">
+        <v>32897.54</v>
       </c>
     </row>
     <row r="31">
@@ -1093,15 +977,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>33568.9</t>
-        </is>
+      <c r="C31" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D31" t="n">
+        <v>33568.9</v>
       </c>
     </row>
     <row r="32">
@@ -1115,15 +995,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>30227.5</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30227.5</v>
       </c>
     </row>
     <row r="33">
@@ -1137,15 +1013,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>26075.35</t>
-        </is>
+      <c r="C33" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D33" t="n">
+        <v>26075.35</v>
       </c>
     </row>
     <row r="34">
@@ -1159,15 +1031,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>23897.58</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>23897.58</v>
       </c>
     </row>
     <row r="35">
@@ -1181,15 +1049,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>25427.71</t>
-        </is>
+      <c r="C35" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25427.71</v>
       </c>
     </row>
     <row r="36">
@@ -1203,15 +1067,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>28027.96</t>
-        </is>
+      <c r="C36" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D36" t="n">
+        <v>28027.96</v>
       </c>
     </row>
     <row r="37">
@@ -1225,15 +1085,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>30398.84</t>
-        </is>
+      <c r="C37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D37" t="n">
+        <v>30398.84</v>
       </c>
     </row>
     <row r="38">
@@ -1247,15 +1103,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>34802.95</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D38" t="n">
+        <v>34802.95</v>
       </c>
     </row>
     <row r="39">
@@ -1269,15 +1121,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>40263.86</t>
-        </is>
+      <c r="C39" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D39" t="n">
+        <v>40263.86</v>
       </c>
     </row>
     <row r="40">
@@ -1291,15 +1139,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>43288.53</t>
-        </is>
+      <c r="C40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D40" t="n">
+        <v>43288.53</v>
       </c>
     </row>
     <row r="41">
@@ -1313,15 +1157,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>43981.02</t>
-        </is>
+      <c r="C41" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D41" t="n">
+        <v>43981.02</v>
       </c>
     </row>
     <row r="42">
@@ -1335,15 +1175,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>32729.52</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D42" t="n">
+        <v>32729.52</v>
       </c>
     </row>
     <row r="43">
@@ -1357,15 +1193,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>36335.8</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D43" t="n">
+        <v>36335.8</v>
       </c>
     </row>
     <row r="44">
@@ -1379,15 +1211,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>40920.92</t>
-        </is>
+      <c r="C44" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D44" t="n">
+        <v>40920.92</v>
       </c>
     </row>
     <row r="45">
@@ -1401,15 +1229,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>45144.32</t>
-        </is>
+      <c r="C45" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D45" t="n">
+        <v>45144.32</v>
       </c>
     </row>
     <row r="46">
@@ -1423,15 +1247,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>51982.58</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D46" t="n">
+        <v>51982.58</v>
       </c>
     </row>
     <row r="47">
@@ -1445,15 +1265,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>55979.78</t>
-        </is>
+      <c r="C47" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D47" t="n">
+        <v>55979.78</v>
       </c>
     </row>
     <row r="48">
@@ -1467,15 +1283,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>61549.24</t>
-        </is>
+      <c r="C48" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D48" t="n">
+        <v>61549.24</v>
       </c>
     </row>
     <row r="49">
@@ -1489,15 +1301,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>66218.96</t>
-        </is>
+      <c r="C49" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D49" t="n">
+        <v>66218.96000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1511,15 +1319,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>66460.18</t>
-        </is>
+      <c r="C50" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D50" t="n">
+        <v>66460.17999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1533,15 +1337,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>70969.32</t>
-        </is>
+      <c r="C51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D51" t="n">
+        <v>70969.32000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1555,15 +1355,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>67068.49</t>
-        </is>
+      <c r="C52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D52" t="n">
+        <v>67068.49000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1577,15 +1373,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>67343.76</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D53" t="n">
+        <v>67343.75999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1599,15 +1391,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>71121.45</t>
-        </is>
+      <c r="C54" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D54" t="n">
+        <v>71121.45</v>
       </c>
     </row>
     <row r="55">
@@ -1621,15 +1409,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>64681.88</t>
-        </is>
+      <c r="C55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D55" t="n">
+        <v>64681.88</v>
       </c>
     </row>
     <row r="56">
@@ -1643,15 +1427,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>57649.66</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D56" t="n">
+        <v>57649.66</v>
       </c>
     </row>
     <row r="57">
@@ -1665,15 +1445,11 @@
           <t>Улсын дүн</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>58104.21</t>
-        </is>
+      <c r="C57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D57" t="n">
+        <v>58104.21</v>
       </c>
     </row>
   </sheetData>
